--- a/Tables/MagnitudeCeilingTest_Macau.xlsx
+++ b/Tables/MagnitudeCeilingTest_Macau.xlsx
@@ -465,37 +465,37 @@
         <v>52</v>
       </c>
       <c r="D2">
-        <v>8.852</v>
+        <v>8.827999999999999</v>
       </c>
       <c r="E2">
-        <v>3.189</v>
+        <v>3.132</v>
       </c>
       <c r="F2">
-        <v>12.623</v>
+        <v>12.611</v>
       </c>
       <c r="G2">
-        <v>1.026</v>
+        <v>1.024</v>
       </c>
       <c r="H2">
-        <v>-4.959</v>
+        <v>-5.068</v>
       </c>
       <c r="I2">
-        <v>3.923</v>
+        <v>3.911</v>
       </c>
       <c r="J2">
-        <v>61.36</v>
+        <v>61.431</v>
       </c>
       <c r="K2">
-        <v>15.385</v>
+        <v>15.337</v>
       </c>
       <c r="L2">
         <v>94.23099999999999</v>
       </c>
       <c r="M2">
-        <v>-0.193</v>
+        <v>-0.196</v>
       </c>
       <c r="N2">
-        <v>0.495</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="3">
@@ -511,25 +511,25 @@
         <v>52</v>
       </c>
       <c r="D3">
-        <v>12.56</v>
+        <v>12.576</v>
       </c>
       <c r="E3">
-        <v>7.201</v>
+        <v>7.399</v>
       </c>
       <c r="F3">
-        <v>14.992</v>
+        <v>14.976</v>
       </c>
       <c r="G3">
-        <v>-0.707</v>
+        <v>-0.709</v>
       </c>
       <c r="H3">
-        <v>-6.692</v>
+        <v>-6.801</v>
       </c>
       <c r="I3">
-        <v>2.189</v>
+        <v>2.177</v>
       </c>
       <c r="J3">
-        <v>43.756</v>
+        <v>43.842</v>
       </c>
       <c r="K3">
         <v>17.308</v>
@@ -538,10 +538,10 @@
         <v>53.846</v>
       </c>
       <c r="M3">
-        <v>0.529</v>
+        <v>0.532</v>
       </c>
       <c r="N3">
-        <v>-0.152</v>
+        <v>-0.148</v>
       </c>
     </row>
     <row r="4">
@@ -557,25 +557,25 @@
         <v>53</v>
       </c>
       <c r="D4">
-        <v>15.514</v>
+        <v>15.505</v>
       </c>
       <c r="E4">
-        <v>8.317</v>
+        <v>8.247999999999999</v>
       </c>
       <c r="F4">
-        <v>19.243</v>
+        <v>19.251</v>
       </c>
       <c r="G4">
-        <v>3.303</v>
+        <v>3.302</v>
       </c>
       <c r="H4">
-        <v>-2.643</v>
+        <v>-2.762</v>
       </c>
       <c r="I4">
-        <v>6.186</v>
+        <v>6.172</v>
       </c>
       <c r="J4">
-        <v>60.319</v>
+        <v>60.449</v>
       </c>
       <c r="K4">
         <v>33.962</v>
@@ -584,10 +584,10 @@
         <v>88.679</v>
       </c>
       <c r="M4">
-        <v>1.104</v>
+        <v>1.101</v>
       </c>
       <c r="N4">
-        <v>0.457</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="5">
@@ -603,25 +603,25 @@
         <v>52</v>
       </c>
       <c r="D5">
-        <v>7.293</v>
+        <v>7.263</v>
       </c>
       <c r="E5">
-        <v>3.196</v>
+        <v>3.183</v>
       </c>
       <c r="F5">
-        <v>9.15</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="G5">
-        <v>-0.016</v>
+        <v>-0.018</v>
       </c>
       <c r="H5">
-        <v>-6.001</v>
+        <v>-6.11</v>
       </c>
       <c r="I5">
-        <v>2.88</v>
+        <v>2.868</v>
       </c>
       <c r="J5">
-        <v>53.171</v>
+        <v>53.119</v>
       </c>
       <c r="K5">
         <v>11.538</v>
@@ -630,10 +630,10 @@
         <v>84.61499999999999</v>
       </c>
       <c r="M5">
-        <v>-0.496</v>
+        <v>-0.5</v>
       </c>
       <c r="N5">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="6">
@@ -649,25 +649,25 @@
         <v>52</v>
       </c>
       <c r="D6">
-        <v>14.36</v>
+        <v>14.375</v>
       </c>
       <c r="E6">
-        <v>8.875999999999999</v>
+        <v>9.051</v>
       </c>
       <c r="F6">
-        <v>18.032</v>
+        <v>18.044</v>
       </c>
       <c r="G6">
-        <v>2.713</v>
+        <v>2.711</v>
       </c>
       <c r="H6">
-        <v>-3.272</v>
+        <v>-3.381</v>
       </c>
       <c r="I6">
-        <v>5.61</v>
+        <v>5.598</v>
       </c>
       <c r="J6">
-        <v>59.529</v>
+        <v>59.531</v>
       </c>
       <c r="K6">
         <v>23.077</v>
@@ -676,10 +676,10 @@
         <v>96.154</v>
       </c>
       <c r="M6">
-        <v>0.88</v>
+        <v>0.881</v>
       </c>
       <c r="N6">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="7">
@@ -695,25 +695,25 @@
         <v>52</v>
       </c>
       <c r="D7">
-        <v>4.94</v>
+        <v>4.944</v>
       </c>
       <c r="E7">
-        <v>-3.522</v>
+        <v>-3.476</v>
       </c>
       <c r="F7">
-        <v>9.045</v>
+        <v>9.031000000000001</v>
       </c>
       <c r="G7">
-        <v>-1.739</v>
+        <v>-1.741</v>
       </c>
       <c r="H7">
-        <v>-7.724</v>
+        <v>-7.833</v>
       </c>
       <c r="I7">
-        <v>1.157</v>
+        <v>1.145</v>
       </c>
       <c r="J7">
-        <v>25.333</v>
+        <v>25.206</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -722,10 +722,10 @@
         <v>53.846</v>
       </c>
       <c r="M7">
-        <v>-0.954</v>
+        <v>-0.95</v>
       </c>
       <c r="N7">
-        <v>-0.829</v>
+        <v>-0.831</v>
       </c>
     </row>
     <row r="8">
@@ -741,37 +741,37 @@
         <v>52</v>
       </c>
       <c r="D8">
-        <v>9.945</v>
+        <v>9.984</v>
       </c>
       <c r="E8">
-        <v>7.172</v>
+        <v>7.298</v>
       </c>
       <c r="F8">
-        <v>11.231</v>
+        <v>11.244</v>
       </c>
       <c r="G8">
-        <v>-1.241</v>
+        <v>-1.243</v>
       </c>
       <c r="H8">
-        <v>-7.225</v>
+        <v>-7.335</v>
       </c>
       <c r="I8">
-        <v>1.656</v>
+        <v>1.644</v>
       </c>
       <c r="J8">
-        <v>34.521</v>
+        <v>34.412</v>
       </c>
       <c r="K8">
         <v>7.692</v>
       </c>
       <c r="L8">
-        <v>63.462</v>
+        <v>61.538</v>
       </c>
       <c r="M8">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="N8">
-        <v>-0.491</v>
+        <v>-0.494</v>
       </c>
     </row>
     <row r="9">
@@ -787,37 +787,37 @@
         <v>53</v>
       </c>
       <c r="D9">
-        <v>4.035</v>
+        <v>4.095</v>
       </c>
       <c r="E9">
-        <v>-3.738</v>
+        <v>-3.699</v>
       </c>
       <c r="F9">
-        <v>8.795</v>
+        <v>8.807</v>
       </c>
       <c r="G9">
-        <v>-1.786</v>
+        <v>-1.788</v>
       </c>
       <c r="H9">
-        <v>-7.733</v>
+        <v>-7.851</v>
       </c>
       <c r="I9">
-        <v>1.096</v>
+        <v>1.083</v>
       </c>
       <c r="J9">
-        <v>16.355</v>
+        <v>16.358</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>52.83</v>
+        <v>50.943</v>
       </c>
       <c r="M9">
-        <v>-1.131</v>
+        <v>-1.115</v>
       </c>
       <c r="N9">
-        <v>-1.16</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="10">
@@ -833,37 +833,37 @@
         <v>52</v>
       </c>
       <c r="D10">
-        <v>4.086</v>
+        <v>3.942</v>
       </c>
       <c r="E10">
-        <v>-1.558</v>
+        <v>-1.837</v>
       </c>
       <c r="F10">
-        <v>6.797</v>
+        <v>6.785</v>
       </c>
       <c r="G10">
-        <v>-1.912</v>
+        <v>-1.914</v>
       </c>
       <c r="H10">
-        <v>-7.897</v>
+        <v>-8.006</v>
       </c>
       <c r="I10">
-        <v>0.985</v>
+        <v>0.972</v>
       </c>
       <c r="J10">
-        <v>29.894</v>
+        <v>29.758</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>55.769</v>
+        <v>57.74</v>
       </c>
       <c r="M10">
-        <v>-1.121</v>
+        <v>-1.144</v>
       </c>
       <c r="N10">
-        <v>-0.662</v>
+        <v>-0.664</v>
       </c>
     </row>
     <row r="11">
@@ -879,25 +879,25 @@
         <v>52</v>
       </c>
       <c r="D11">
-        <v>16.832</v>
+        <v>16.847</v>
       </c>
       <c r="E11">
-        <v>11.393</v>
+        <v>11.602</v>
       </c>
       <c r="F11">
-        <v>19.832</v>
+        <v>19.818</v>
       </c>
       <c r="G11">
-        <v>7.418</v>
+        <v>7.416</v>
       </c>
       <c r="H11">
-        <v>1.433</v>
+        <v>1.324</v>
       </c>
       <c r="I11">
-        <v>10.314</v>
+        <v>10.302</v>
       </c>
       <c r="J11">
-        <v>94.627</v>
+        <v>94.633</v>
       </c>
       <c r="K11">
         <v>71.154</v>
@@ -909,7 +909,7 @@
         <v>1.361</v>
       </c>
       <c r="N11">
-        <v>1.719</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="12">
@@ -925,37 +925,37 @@
         <v>53</v>
       </c>
       <c r="D12">
-        <v>30.125</v>
+        <v>30.08</v>
       </c>
       <c r="E12">
-        <v>24.159</v>
+        <v>24.041</v>
       </c>
       <c r="F12">
-        <v>32.871</v>
+        <v>32.856</v>
       </c>
       <c r="G12">
-        <v>7.865</v>
+        <v>7.863</v>
       </c>
       <c r="H12">
-        <v>1.918</v>
+        <v>1.8</v>
       </c>
       <c r="I12">
-        <v>10.747</v>
+        <v>10.734</v>
       </c>
       <c r="J12">
-        <v>91.045</v>
+        <v>91.096</v>
       </c>
       <c r="K12">
-        <v>49.057</v>
+        <v>49.009</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>3.949</v>
+        <v>3.931</v>
       </c>
       <c r="N12">
-        <v>1.587</v>
+        <v>1.585</v>
       </c>
       <c r="O12">
         <v>0.999</v>
@@ -967,10 +967,10 @@
         <v>1</v>
       </c>
       <c r="R12">
-        <v>0.9076</v>
+        <v>0.9069</v>
       </c>
       <c r="S12">
-        <v>1.79</v>
+        <v>1.786</v>
       </c>
     </row>
     <row r="13">
@@ -986,37 +986,37 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>15.458</v>
+        <v>15.179</v>
       </c>
       <c r="E13">
-        <v>10.827</v>
+        <v>10.334</v>
       </c>
       <c r="F13">
-        <v>17.501</v>
+        <v>17.403</v>
       </c>
       <c r="G13">
-        <v>1.204</v>
+        <v>1.202</v>
       </c>
       <c r="H13">
-        <v>-4.781</v>
+        <v>-4.89</v>
       </c>
       <c r="I13">
-        <v>4.1</v>
+        <v>4.088</v>
       </c>
       <c r="J13">
-        <v>52.2</v>
+        <v>51.796</v>
       </c>
       <c r="K13">
-        <v>11.538</v>
+        <v>9.615</v>
       </c>
       <c r="L13">
-        <v>86.538</v>
+        <v>88.462</v>
       </c>
       <c r="M13">
-        <v>1.094</v>
+        <v>1.037</v>
       </c>
       <c r="N13">
-        <v>0.159</v>
+        <v>0.144</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0.8287</v>
+        <v>0.8157</v>
       </c>
       <c r="R13">
-        <v>0.6161</v>
+        <v>0.5597</v>
       </c>
       <c r="S13">
-        <v>0.918</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="14">
@@ -1047,25 +1047,25 @@
         <v>35</v>
       </c>
       <c r="D14">
-        <v>4.224</v>
+        <v>4.252</v>
       </c>
       <c r="E14">
-        <v>-0.407</v>
+        <v>-0.21</v>
       </c>
       <c r="F14">
-        <v>6.266</v>
+        <v>6.269</v>
       </c>
       <c r="G14">
-        <v>-2.524</v>
+        <v>-2.528</v>
       </c>
       <c r="H14">
-        <v>-9.680999999999999</v>
+        <v>-9.691000000000001</v>
       </c>
       <c r="I14">
-        <v>0.951</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="J14">
-        <v>21.174</v>
+        <v>21.151</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>57.143</v>
       </c>
       <c r="M14">
-        <v>-1.094</v>
+        <v>-1.084</v>
       </c>
       <c r="N14">
-        <v>-0.982</v>
+        <v>-0.98</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1086,13 +1086,13 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0.1297</v>
+        <v>0.1321</v>
       </c>
       <c r="R14">
-        <v>0.2006</v>
+        <v>0.1871</v>
       </c>
       <c r="S14">
-        <v>0.251</v>
+        <v>0.252</v>
       </c>
     </row>
   </sheetData>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.637</t>
+          <t>9.659</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17.043</t>
+          <t>17.03</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17.978</t>
+          <t>17.968</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18.642</t>
+          <t>18.644</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>9.008</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9.842</t>
+          <t>9.836</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.136</t>
+          <t>5.15</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>47.886</t>
+          <t>47.874</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27.193</t>
+          <t>27.277</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16.832</t>
+          <t>16.847</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11.393</t>
+          <t>11.602</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19.832</t>
+          <t>19.818</t>
         </is>
       </c>
     </row>
